--- a/RocioCordoba/02_ObispoSalguero387_13C/MesesPagados_ObispoSalguero387_13C.xlsx
+++ b/RocioCordoba/02_ObispoSalguero387_13C/MesesPagados_ObispoSalguero387_13C.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\RocioCordoba\02_ObispoSalguero387_13C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685E3EB2-0093-43F1-8EB2-156A4737A9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232F00C5-1C20-4BD1-BBCD-A577767E3F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31125" yWindow="1695" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -559,6 +559,23 @@
         <v>888908.26</v>
       </c>
     </row>
+    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>2026</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1">
+        <v>816084</v>
+      </c>
+      <c r="F10" s="1">
+        <v>816084</v>
+      </c>
+      <c r="G10" s="1">
+        <v>142865.96</v>
+      </c>
+    </row>
     <row r="16" spans="3:11" x14ac:dyDescent="0.25">
       <c r="F16" s="4" t="s">
         <v>9</v>
@@ -572,7 +589,7 @@
         <v>7</v>
       </c>
       <c r="G17" s="1">
-        <v>748951</v>
+        <v>816084</v>
       </c>
     </row>
     <row r="18" spans="6:7" x14ac:dyDescent="0.25">
@@ -580,7 +597,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>139957.26</v>
+        <v>142865.96</v>
       </c>
     </row>
     <row r="20" spans="6:7" x14ac:dyDescent="0.25">
@@ -589,7 +606,7 @@
       </c>
       <c r="G20" s="1">
         <f>+G17+G18</f>
-        <v>888908.26</v>
+        <v>958949.96</v>
       </c>
     </row>
     <row r="22" spans="6:7" x14ac:dyDescent="0.25">
@@ -598,7 +615,7 @@
       </c>
       <c r="G22" s="1">
         <f>+G20/2</f>
-        <v>444454.13</v>
+        <v>479474.98</v>
       </c>
     </row>
   </sheetData>

--- a/RocioCordoba/02_ObispoSalguero387_13C/MesesPagados_ObispoSalguero387_13C.xlsx
+++ b/RocioCordoba/02_ObispoSalguero387_13C/MesesPagados_ObispoSalguero387_13C.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\RocioCordoba\02_ObispoSalguero387_13C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232F00C5-1C20-4BD1-BBCD-A577767E3F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7186C352-6383-4F2E-8754-86544BD79093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31125" yWindow="1695" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6150" yWindow="3165" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>AÑO</t>
   </si>
@@ -61,14 +61,21 @@
   </si>
   <si>
     <t>Cada uno</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>AUMENTO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="[$$-2C0A]\ #,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -119,12 +126,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,17 +414,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:K22"/>
+  <dimension ref="B3:K22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -432,7 +446,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="J3" s="2"/>
@@ -440,7 +454,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C4">
         <v>2026</v>
       </c>
@@ -458,7 +472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>2026</v>
       </c>
@@ -476,7 +490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C6">
         <v>2026</v>
       </c>
@@ -494,7 +508,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
       <c r="C7">
         <v>2026</v>
       </c>
@@ -512,7 +529,7 @@
         <v>48951</v>
       </c>
     </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C8">
         <v>2026</v>
       </c>
@@ -529,7 +546,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="6">
         <v>140891.47</v>
       </c>
       <c r="K8" s="1">
@@ -537,7 +554,7 @@
         <v>889842.47</v>
       </c>
     </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C9">
         <v>2026</v>
       </c>
@@ -551,15 +568,15 @@
         <f>+E9</f>
         <v>748951</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="6">
         <v>139957.26</v>
       </c>
-      <c r="K9" s="1">
-        <f>+E9+I9</f>
-        <v>888908.26</v>
-      </c>
-    </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
       <c r="C10">
         <v>2026</v>
       </c>
@@ -575,8 +592,27 @@
       <c r="G10" s="1">
         <v>142865.96</v>
       </c>
-    </row>
-    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>2026</v>
+      </c>
+      <c r="D11">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1">
+        <v>816084</v>
+      </c>
+      <c r="I11" s="6">
+        <v>142865.96</v>
+      </c>
+      <c r="K11" s="1">
+        <f t="shared" ref="K10:K11" si="1">+E11+I11</f>
+        <v>958949.96</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F16" s="4" t="s">
         <v>9</v>
       </c>

--- a/RocioCordoba/02_ObispoSalguero387_13C/MesesPagados_ObispoSalguero387_13C.xlsx
+++ b/RocioCordoba/02_ObispoSalguero387_13C/MesesPagados_ObispoSalguero387_13C.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\RocioCordoba\02_ObispoSalguero387_13C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7186C352-6383-4F2E-8754-86544BD79093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CA353E-94C9-436E-A68D-56F91D6469E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6150" yWindow="3165" windowWidth="21600" windowHeight="12690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -113,6 +113,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -126,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -134,6 +140,7 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -608,8 +615,19 @@
         <v>142865.96</v>
       </c>
       <c r="K11" s="1">
-        <f t="shared" ref="K10:K11" si="1">+E11+I11</f>
+        <f t="shared" ref="K11" si="1">+E11+I11</f>
         <v>958949.96</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C12">
+        <v>2026</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1">
+        <v>816084</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
@@ -633,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>142865.96</v>
+        <v>144457.26</v>
       </c>
     </row>
     <row r="20" spans="6:7" x14ac:dyDescent="0.25">
@@ -642,16 +660,16 @@
       </c>
       <c r="G20" s="1">
         <f>+G17+G18</f>
-        <v>958949.96</v>
+        <v>960541.26</v>
       </c>
     </row>
     <row r="22" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="7">
         <f>+G20/2</f>
-        <v>479474.98</v>
+        <v>480270.63</v>
       </c>
     </row>
   </sheetData>
